--- a/Resources/Sample/FBCD.xlsx
+++ b/Resources/Sample/FBCD.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="683" uniqueCount="289">
   <si>
     <t>tk</t>
   </si>
@@ -70,12 +70,48 @@
     <t>SO DU NO</t>
   </si>
   <si>
+    <t>1111</t>
+  </si>
+  <si>
+    <t>TIEN VIET NAM</t>
+  </si>
+  <si>
+    <t>1112</t>
+  </si>
+  <si>
+    <t>TIEN NGOAI TE</t>
+  </si>
+  <si>
+    <t>1113</t>
+  </si>
+  <si>
+    <t>VANG BAC, DA QUY</t>
+  </si>
+  <si>
     <t>112</t>
   </si>
   <si>
     <t>TIEN GUI NGAN HANG</t>
   </si>
   <si>
+    <t>1121</t>
+  </si>
+  <si>
+    <t>TIEN GUI VIET NAM</t>
+  </si>
+  <si>
+    <t>1122</t>
+  </si>
+  <si>
+    <t>TIEN GUI NGOAI TE</t>
+  </si>
+  <si>
+    <t>1123</t>
+  </si>
+  <si>
+    <t>TIEN GUI VANG BAC, DA QUY</t>
+  </si>
+  <si>
     <t>121</t>
   </si>
   <si>
@@ -94,18 +130,81 @@
     <t>1</t>
   </si>
   <si>
+    <t>1311</t>
+  </si>
+  <si>
+    <t>PHAI THU CUA KHACH HANG NGAN HAN</t>
+  </si>
+  <si>
+    <t>HET THUC H</t>
+  </si>
+  <si>
+    <t>1312</t>
+  </si>
+  <si>
+    <t>PHAI THU CUA KHACH HANG DAI HAN</t>
+  </si>
+  <si>
+    <t>CON THUC H</t>
+  </si>
+  <si>
     <t>133</t>
   </si>
   <si>
     <t>THUE GTGT DUOC KHAU TRU</t>
   </si>
   <si>
+    <t>1331</t>
+  </si>
+  <si>
+    <t>THUE GTGT DUOC KHAU TRU CUA HANG HOA</t>
+  </si>
+  <si>
+    <t>1332</t>
+  </si>
+  <si>
+    <t>THUE GTGT DUOC KHAU TRU CUA TSCD</t>
+  </si>
+  <si>
     <t>138</t>
   </si>
   <si>
     <t>PHAI THU KHAC</t>
   </si>
   <si>
+    <t>1381</t>
+  </si>
+  <si>
+    <t>TAI SAN THIEU CHO XU LY</t>
+  </si>
+  <si>
+    <t>1388</t>
+  </si>
+  <si>
+    <t>138811</t>
+  </si>
+  <si>
+    <t>PHAI THU KHAC NGAN HAN</t>
+  </si>
+  <si>
+    <t>138812</t>
+  </si>
+  <si>
+    <t>PHAI THU KHAC DAI HAN</t>
+  </si>
+  <si>
+    <t>138821</t>
+  </si>
+  <si>
+    <t>KY QUY KY CUOC NGAN HAN</t>
+  </si>
+  <si>
+    <t>138822</t>
+  </si>
+  <si>
+    <t>KY QUY KY CUOC DAI HAN</t>
+  </si>
+  <si>
     <t>141</t>
   </si>
   <si>
@@ -118,7 +217,19 @@
     <t>CHI PHI TRA TRUOC NGAN HAN</t>
   </si>
   <si>
-    <t>HET THUC H</t>
+    <t>1421</t>
+  </si>
+  <si>
+    <t>CHI PHI QUANG CAO TRA TRUOC</t>
+  </si>
+  <si>
+    <t>THUC HIEN</t>
+  </si>
+  <si>
+    <t>1422</t>
+  </si>
+  <si>
+    <t>CHI PHI TRA TRUOC KHAC</t>
   </si>
   <si>
     <t>152</t>
@@ -151,6 +262,18 @@
     <t>HANG HOA</t>
   </si>
   <si>
+    <t>1561</t>
+  </si>
+  <si>
+    <t>GIA MUA HANG HOA</t>
+  </si>
+  <si>
+    <t>1562</t>
+  </si>
+  <si>
+    <t>CHI PHI MUA HANG HOA</t>
+  </si>
+  <si>
     <t>157</t>
   </si>
   <si>
@@ -163,12 +286,48 @@
     <t>CAC KHOAN DU PHONG</t>
   </si>
   <si>
+    <t>1591</t>
+  </si>
+  <si>
+    <t>DU PHONG GIAM GIA DAU TU TAI CHINH NGAN HAN</t>
+  </si>
+  <si>
+    <t>1592</t>
+  </si>
+  <si>
+    <t>DU PHONG PHAI THU KHO DOI</t>
+  </si>
+  <si>
+    <t>1593</t>
+  </si>
+  <si>
+    <t>DU PHONG GIAM GIA HANG TON KHO</t>
+  </si>
+  <si>
     <t>211</t>
   </si>
   <si>
     <t>TAI SAN CO DINH</t>
   </si>
   <si>
+    <t>2111</t>
+  </si>
+  <si>
+    <t>TAI SAN CO DINH HUU HINH</t>
+  </si>
+  <si>
+    <t>2112</t>
+  </si>
+  <si>
+    <t>TAI SAN CO DINH THUE TAI CHINH</t>
+  </si>
+  <si>
+    <t>2113</t>
+  </si>
+  <si>
+    <t>TAI SAN CO DINH VO HINH</t>
+  </si>
+  <si>
     <t>214</t>
   </si>
   <si>
@@ -181,6 +340,30 @@
     <t>SO DU CO</t>
   </si>
   <si>
+    <t>2141</t>
+  </si>
+  <si>
+    <t>HAO MON TAI SAN CO DINH HUU HINH</t>
+  </si>
+  <si>
+    <t>2142</t>
+  </si>
+  <si>
+    <t>HAO MON TAI SAN CO DINH THUE TAI CHINH</t>
+  </si>
+  <si>
+    <t>2143</t>
+  </si>
+  <si>
+    <t>HAO MON TAI SAN CO DINH VO HINH</t>
+  </si>
+  <si>
+    <t>2147</t>
+  </si>
+  <si>
+    <t>HAO MON TAI SAN CO DINH DAU TU BAT DONG SAN</t>
+  </si>
+  <si>
     <t>217</t>
   </si>
   <si>
@@ -193,7 +376,22 @@
     <t>DAU TU TAI CHINH DAI HAN</t>
   </si>
   <si>
-    <t>CON THUC H</t>
+    <t>2212</t>
+  </si>
+  <si>
+    <t>VON GOP LIEN DOANH</t>
+  </si>
+  <si>
+    <t>2213</t>
+  </si>
+  <si>
+    <t>DAU TU VAO CONG TY LIEN KET</t>
+  </si>
+  <si>
+    <t>2218</t>
+  </si>
+  <si>
+    <t>DAU TU TAI CHINH DAI HAN KHAC</t>
   </si>
   <si>
     <t>229</t>
@@ -208,18 +406,39 @@
     <t>XAY DUNG CO BAN DO DANG</t>
   </si>
   <si>
+    <t>2411</t>
+  </si>
+  <si>
+    <t>MUA SAM TSCD DO DANG</t>
+  </si>
+  <si>
+    <t>2412</t>
+  </si>
+  <si>
+    <t>2413</t>
+  </si>
+  <si>
+    <t>SUA CHUA LON TAI SAN CO DINH DO DANG</t>
+  </si>
+  <si>
     <t>242</t>
   </si>
   <si>
     <t>CHI PHI TRA TRUOC DAI HAN</t>
   </si>
   <si>
+    <t>2421</t>
+  </si>
+  <si>
+    <t>CHI PHI TRA TRUOC -QUANG CAO</t>
+  </si>
+  <si>
+    <t>2422</t>
+  </si>
+  <si>
     <t>244</t>
   </si>
   <si>
-    <t>KY QUY KY CUOC DAI HAN</t>
-  </si>
-  <si>
     <t>311</t>
   </si>
   <si>
@@ -241,12 +460,90 @@
     <t>SDU CO, NO</t>
   </si>
   <si>
+    <t>3311</t>
+  </si>
+  <si>
+    <t>PHAI TRA CHO NHA CUNG CAP NGAN HAN</t>
+  </si>
+  <si>
+    <t>3312</t>
+  </si>
+  <si>
+    <t>PHAI TRA CHO NHA CUNG CAP DAI HAN</t>
+  </si>
+  <si>
     <t>333</t>
   </si>
   <si>
     <t>THUE PHAI NOP NGAN SACH NHA NUOC</t>
   </si>
   <si>
+    <t>3331</t>
+  </si>
+  <si>
+    <t>THUE GTGT PHAI NOP</t>
+  </si>
+  <si>
+    <t>33311</t>
+  </si>
+  <si>
+    <t>THUE GTGT DAU RA</t>
+  </si>
+  <si>
+    <t>33312</t>
+  </si>
+  <si>
+    <t>THUE GTGT HANG NHAP KHAU</t>
+  </si>
+  <si>
+    <t>3332</t>
+  </si>
+  <si>
+    <t>THUE TIEU THU DAC BIET</t>
+  </si>
+  <si>
+    <t>3333</t>
+  </si>
+  <si>
+    <t>THUE XUAT NHAP KHAU</t>
+  </si>
+  <si>
+    <t>3334</t>
+  </si>
+  <si>
+    <t>THUE THU NHAP DOANH NGHIEP</t>
+  </si>
+  <si>
+    <t>3335</t>
+  </si>
+  <si>
+    <t>THUE THU NHAP CA NHAN</t>
+  </si>
+  <si>
+    <t>3336</t>
+  </si>
+  <si>
+    <t>THUE TAI NGUYEN</t>
+  </si>
+  <si>
+    <t>3337</t>
+  </si>
+  <si>
+    <t>THUE NHA DAT , TIEN THUE DAT</t>
+  </si>
+  <si>
+    <t>3338</t>
+  </si>
+  <si>
+    <t>CAC LOAI THUE KHAC</t>
+  </si>
+  <si>
+    <t>3339</t>
+  </si>
+  <si>
+    <t>PHI, LE PHI VA CAC KHOAN PHAI NOP KHAC</t>
+  </si>
+  <si>
     <t>334</t>
   </si>
   <si>
@@ -265,12 +562,108 @@
     <t>PHAI TRA, PHAI NOP KHAC</t>
   </si>
   <si>
+    <t>3381</t>
+  </si>
+  <si>
+    <t>TAI SAN THUA CHO GIAI QUYET</t>
+  </si>
+  <si>
+    <t>3382</t>
+  </si>
+  <si>
+    <t>KINH PHI CONG DOAN</t>
+  </si>
+  <si>
+    <t>3383</t>
+  </si>
+  <si>
+    <t>BAO HIEM XA HOI</t>
+  </si>
+  <si>
+    <t>3384</t>
+  </si>
+  <si>
+    <t>BAO HIEM Y TE</t>
+  </si>
+  <si>
+    <t>3386</t>
+  </si>
+  <si>
+    <t>NHAN KY QUY KY CUOC NGAN HAN</t>
+  </si>
+  <si>
+    <t>3387</t>
+  </si>
+  <si>
+    <t>DOANH THU CHUA THUC HIEN</t>
+  </si>
+  <si>
+    <t>3388</t>
+  </si>
+  <si>
+    <t>PHAI TRA PHAI NOP KHAC</t>
+  </si>
+  <si>
+    <t>33881</t>
+  </si>
+  <si>
+    <t>PHAI TRA PHAI NOP NGAN HAN</t>
+  </si>
+  <si>
+    <t>33882</t>
+  </si>
+  <si>
+    <t>PHAI TRA PHAI NOP DAI HAN</t>
+  </si>
+  <si>
     <t>341</t>
   </si>
   <si>
     <t>VAY, NO DAI HAN</t>
   </si>
   <si>
+    <t>3411</t>
+  </si>
+  <si>
+    <t>VAY DAI HAN</t>
+  </si>
+  <si>
+    <t>3412</t>
+  </si>
+  <si>
+    <t>NO DAI HAN</t>
+  </si>
+  <si>
+    <t>3413</t>
+  </si>
+  <si>
+    <t>TRAI PHIEU PHAT HANH</t>
+  </si>
+  <si>
+    <t>34131</t>
+  </si>
+  <si>
+    <t>MENH GIA TRAI PHIEU</t>
+  </si>
+  <si>
+    <t>34132</t>
+  </si>
+  <si>
+    <t>CHIET KHAU TRAI PHIEU</t>
+  </si>
+  <si>
+    <t>34133</t>
+  </si>
+  <si>
+    <t>PHU TROI TRAI PHIEU</t>
+  </si>
+  <si>
+    <t>3414</t>
+  </si>
+  <si>
+    <t>NHAN KY QUY , KY CUOC DAI HAN</t>
+  </si>
+  <si>
     <t>351</t>
   </si>
   <si>
@@ -283,12 +676,42 @@
     <t>DU PHONG PHAI TRA</t>
   </si>
   <si>
+    <t>3521</t>
+  </si>
+  <si>
+    <t>DU PHONG PHAI TRA NGAN HAN</t>
+  </si>
+  <si>
+    <t>3522</t>
+  </si>
+  <si>
+    <t>DU PHONG PHAI TRA DAI HAN</t>
+  </si>
+  <si>
     <t>411</t>
   </si>
   <si>
     <t>NGUON VON KINH DOANH</t>
   </si>
   <si>
+    <t>4111</t>
+  </si>
+  <si>
+    <t>VON DAU TU CUA CHU SO HUU</t>
+  </si>
+  <si>
+    <t>4112</t>
+  </si>
+  <si>
+    <t>THANG DU VON CO PHAN</t>
+  </si>
+  <si>
+    <t>4118</t>
+  </si>
+  <si>
+    <t>VON KHAC</t>
+  </si>
+  <si>
     <t>413</t>
   </si>
   <si>
@@ -313,12 +736,36 @@
     <t>LOI NHUAN CHUA PHAN PHOI</t>
   </si>
   <si>
+    <t>4211</t>
+  </si>
+  <si>
+    <t>LOI NHUAN CHUA PHAN PHOI NAM TRUOC</t>
+  </si>
+  <si>
+    <t>4212</t>
+  </si>
+  <si>
+    <t>LOI NHUAN CHUA PHAN PHOI NAM NAY</t>
+  </si>
+  <si>
     <t>431</t>
   </si>
   <si>
     <t>QUY KHEN THUONG, PHUC LOI</t>
   </si>
   <si>
+    <t>4311</t>
+  </si>
+  <si>
+    <t>QUY KHEN THUONG</t>
+  </si>
+  <si>
+    <t>4312</t>
+  </si>
+  <si>
+    <t>QUY PHUC LOI</t>
+  </si>
+  <si>
     <t>511</t>
   </si>
   <si>
@@ -328,6 +775,30 @@
     <t>O CO SDU</t>
   </si>
   <si>
+    <t>5111</t>
+  </si>
+  <si>
+    <t>DOANH THU BAN HANG HOA</t>
+  </si>
+  <si>
+    <t>5112</t>
+  </si>
+  <si>
+    <t>DOANH THU BAN THANH PHAM</t>
+  </si>
+  <si>
+    <t>5113</t>
+  </si>
+  <si>
+    <t>DOANH THU CUNG CAP DICH VU</t>
+  </si>
+  <si>
+    <t>5118</t>
+  </si>
+  <si>
+    <t>DOANH THU KHAC</t>
+  </si>
+  <si>
     <t>515</t>
   </si>
   <si>
@@ -340,6 +811,24 @@
     <t>CAC KHOAN GIAM TRU DOANH THU</t>
   </si>
   <si>
+    <t>5211</t>
+  </si>
+  <si>
+    <t>CHIET KHAU THUONG MAI</t>
+  </si>
+  <si>
+    <t>5212</t>
+  </si>
+  <si>
+    <t>HANG BAN BI TRA LAI</t>
+  </si>
+  <si>
+    <t>5213</t>
+  </si>
+  <si>
+    <t>GIAM GIA HANG BAN</t>
+  </si>
+  <si>
     <t>632</t>
   </si>
   <si>
@@ -356,6 +845,18 @@
   </si>
   <si>
     <t>CHI PHI QUAN LY KINH DOANH</t>
+  </si>
+  <si>
+    <t>6421</t>
+  </si>
+  <si>
+    <t>CHI PHI BAN HANG</t>
+  </si>
+  <si>
+    <t>6422</t>
+  </si>
+  <si>
+    <t>CHI PHI QUAN LY DOANH NGHIEP</t>
   </si>
   <si>
     <t>711</t>
@@ -387,9 +888,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
   </numFmts>
   <fonts count="20">
@@ -401,24 +902,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF0000FF"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -431,17 +917,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -455,11 +932,33 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="18"/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="Calibri"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -479,39 +978,26 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <i/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF7F7F7F"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -524,7 +1010,22 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -554,7 +1055,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -566,7 +1097,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -578,13 +1133,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -596,31 +1157,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -638,103 +1223,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -745,21 +1246,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -774,6 +1260,15 @@
       </top>
       <bottom style="double">
         <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -826,11 +1321,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -848,148 +1349,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="16" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="17" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1314,7 +1815,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M50"/>
+  <dimension ref="A1:M135"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="7.57142857142857" customWidth="1"/>
@@ -1380,12 +1881,6 @@
       <c r="B2" t="s">
         <v>14</v>
       </c>
-      <c r="I2">
-        <v>0</v>
-      </c>
-      <c r="J2">
-        <v>0</v>
-      </c>
       <c r="K2" t="s">
         <v>15</v>
       </c>
@@ -1403,12 +1898,6 @@
       <c r="B3" t="s">
         <v>19</v>
       </c>
-      <c r="I3">
-        <v>0</v>
-      </c>
-      <c r="J3">
-        <v>0</v>
-      </c>
       <c r="K3" t="s">
         <v>15</v>
       </c>
@@ -1426,12 +1915,6 @@
       <c r="B4" t="s">
         <v>21</v>
       </c>
-      <c r="I4">
-        <v>0</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
       <c r="K4" t="s">
         <v>15</v>
       </c>
@@ -1449,17 +1932,11 @@
       <c r="B5" t="s">
         <v>23</v>
       </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
       <c r="K5" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="L5" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="M5" t="s">
         <v>16</v>
@@ -1467,16 +1944,10 @@
     </row>
     <row r="6" spans="1:13">
       <c r="A6" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B6" t="s">
-        <v>27</v>
-      </c>
-      <c r="I6">
-        <v>0</v>
-      </c>
-      <c r="J6">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K6" t="s">
         <v>15</v>
@@ -1490,22 +1961,16 @@
     </row>
     <row r="7" spans="1:13">
       <c r="A7" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B7" t="s">
-        <v>29</v>
-      </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="K7" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="L7" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="M7" t="s">
         <v>16</v>
@@ -1513,22 +1978,16 @@
     </row>
     <row r="8" spans="1:13">
       <c r="A8" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B8" t="s">
-        <v>31</v>
-      </c>
-      <c r="I8">
-        <v>0</v>
-      </c>
-      <c r="J8">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="K8" t="s">
         <v>15</v>
       </c>
       <c r="L8" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="M8" t="s">
         <v>16</v>
@@ -1536,45 +1995,33 @@
     </row>
     <row r="9" spans="1:13">
       <c r="A9" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B9" t="s">
-        <v>33</v>
-      </c>
-      <c r="I9">
-        <v>0</v>
-      </c>
-      <c r="J9">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="K9" t="s">
         <v>15</v>
       </c>
       <c r="L9" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="M9" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:13">
       <c r="A10" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B10" t="s">
-        <v>36</v>
-      </c>
-      <c r="I10">
-        <v>0</v>
-      </c>
-      <c r="J10">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="K10" t="s">
         <v>15</v>
       </c>
       <c r="L10" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="M10" t="s">
         <v>16</v>
@@ -1582,22 +2029,16 @@
     </row>
     <row r="11" spans="1:13">
       <c r="A11" t="s">
+        <v>34</v>
+      </c>
+      <c r="B11" t="s">
+        <v>35</v>
+      </c>
+      <c r="K11" t="s">
+        <v>36</v>
+      </c>
+      <c r="L11" t="s">
         <v>37</v>
-      </c>
-      <c r="B11" t="s">
-        <v>38</v>
-      </c>
-      <c r="I11">
-        <v>0</v>
-      </c>
-      <c r="J11">
-        <v>0</v>
-      </c>
-      <c r="K11" t="s">
-        <v>15</v>
-      </c>
-      <c r="L11" t="s">
-        <v>16</v>
       </c>
       <c r="M11" t="s">
         <v>16</v>
@@ -1605,25 +2046,19 @@
     </row>
     <row r="12" spans="1:13">
       <c r="A12" t="s">
+        <v>38</v>
+      </c>
+      <c r="B12" t="s">
         <v>39</v>
       </c>
-      <c r="B12" t="s">
+      <c r="K12" t="s">
+        <v>36</v>
+      </c>
+      <c r="L12" t="s">
+        <v>16</v>
+      </c>
+      <c r="M12" t="s">
         <v>40</v>
-      </c>
-      <c r="I12">
-        <v>0</v>
-      </c>
-      <c r="J12">
-        <v>0</v>
-      </c>
-      <c r="K12" t="s">
-        <v>15</v>
-      </c>
-      <c r="L12" t="s">
-        <v>25</v>
-      </c>
-      <c r="M12" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="13" spans="1:13">
@@ -1633,40 +2068,28 @@
       <c r="B13" t="s">
         <v>42</v>
       </c>
-      <c r="I13">
-        <v>0</v>
-      </c>
-      <c r="J13">
-        <v>0</v>
-      </c>
       <c r="K13" t="s">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="L13" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="M13" t="s">
-        <v>16</v>
+        <v>43</v>
       </c>
     </row>
     <row r="14" spans="1:13">
       <c r="A14" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B14" t="s">
-        <v>44</v>
-      </c>
-      <c r="I14">
-        <v>0</v>
-      </c>
-      <c r="J14">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="K14" t="s">
         <v>15</v>
       </c>
       <c r="L14" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="M14" t="s">
         <v>16</v>
@@ -1674,22 +2097,16 @@
     </row>
     <row r="15" spans="1:13">
       <c r="A15" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B15" t="s">
-        <v>46</v>
-      </c>
-      <c r="I15">
-        <v>0</v>
-      </c>
-      <c r="J15">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="K15" t="s">
         <v>15</v>
       </c>
       <c r="L15" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="M15" t="s">
         <v>16</v>
@@ -1697,22 +2114,16 @@
     </row>
     <row r="16" spans="1:13">
       <c r="A16" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B16" t="s">
-        <v>48</v>
-      </c>
-      <c r="I16">
-        <v>0</v>
-      </c>
-      <c r="J16">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="K16" t="s">
         <v>15</v>
       </c>
       <c r="L16" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="M16" t="s">
         <v>16</v>
@@ -1720,22 +2131,16 @@
     </row>
     <row r="17" spans="1:13">
       <c r="A17" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B17" t="s">
-        <v>50</v>
-      </c>
-      <c r="I17">
-        <v>0</v>
-      </c>
-      <c r="J17">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="K17" t="s">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="L17" t="s">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="M17" t="s">
         <v>16</v>
@@ -1743,45 +2148,33 @@
     </row>
     <row r="18" spans="1:13">
       <c r="A18" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B18" t="s">
-        <v>52</v>
-      </c>
-      <c r="I18">
-        <v>0</v>
-      </c>
-      <c r="J18">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="K18" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="L18" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="M18" t="s">
-        <v>54</v>
+        <v>16</v>
       </c>
     </row>
     <row r="19" spans="1:13">
       <c r="A19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B19" t="s">
-        <v>56</v>
-      </c>
-      <c r="I19">
-        <v>0</v>
-      </c>
-      <c r="J19">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="K19" t="s">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="L19" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="M19" t="s">
         <v>16</v>
@@ -1789,206 +2182,152 @@
     </row>
     <row r="20" spans="1:13">
       <c r="A20" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B20" t="s">
-        <v>58</v>
-      </c>
-      <c r="I20">
-        <v>0</v>
-      </c>
-      <c r="J20">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="K20" t="s">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="L20" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="M20" t="s">
-        <v>59</v>
+        <v>40</v>
       </c>
     </row>
     <row r="21" spans="1:13">
       <c r="A21" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B21" t="s">
-        <v>61</v>
-      </c>
-      <c r="I21">
-        <v>0</v>
-      </c>
-      <c r="J21">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="K21" t="s">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="L21" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="M21" t="s">
-        <v>59</v>
+        <v>43</v>
       </c>
     </row>
     <row r="22" spans="1:13">
       <c r="A22" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B22" t="s">
-        <v>63</v>
-      </c>
-      <c r="I22">
-        <v>0</v>
-      </c>
-      <c r="J22">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="K22" t="s">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="L22" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="M22" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
     </row>
     <row r="23" spans="1:13">
       <c r="A23" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B23" t="s">
-        <v>65</v>
-      </c>
-      <c r="I23">
-        <v>0</v>
-      </c>
-      <c r="J23">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="K23" t="s">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="L23" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="M23" t="s">
-        <v>59</v>
+        <v>43</v>
       </c>
     </row>
     <row r="24" spans="1:13">
       <c r="A24" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B24" t="s">
-        <v>67</v>
-      </c>
-      <c r="I24">
-        <v>0</v>
-      </c>
-      <c r="J24">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="K24" t="s">
         <v>15</v>
       </c>
       <c r="L24" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="M24" t="s">
-        <v>59</v>
+        <v>16</v>
       </c>
     </row>
     <row r="25" spans="1:13">
       <c r="A25" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B25" t="s">
-        <v>69</v>
-      </c>
-      <c r="I25">
-        <v>0</v>
-      </c>
-      <c r="J25">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="K25" t="s">
-        <v>53</v>
+        <v>15</v>
       </c>
       <c r="L25" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="M25" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
     </row>
     <row r="26" spans="1:13">
       <c r="A26" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B26" t="s">
-        <v>71</v>
-      </c>
-      <c r="I26">
-        <v>0</v>
-      </c>
-      <c r="J26">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="K26" t="s">
-        <v>53</v>
+        <v>15</v>
       </c>
       <c r="L26" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="M26" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
     </row>
     <row r="27" spans="1:13">
       <c r="A27" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B27" t="s">
-        <v>73</v>
-      </c>
-      <c r="I27">
-        <v>0</v>
-      </c>
-      <c r="J27">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="K27" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="L27" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="M27" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
     </row>
     <row r="28" spans="1:13">
       <c r="A28" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B28" t="s">
-        <v>76</v>
-      </c>
-      <c r="I28">
-        <v>0</v>
-      </c>
-      <c r="J28">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="K28" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="L28" t="s">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="M28" t="s">
         <v>16</v>
@@ -1996,19 +2335,13 @@
     </row>
     <row r="29" spans="1:13">
       <c r="A29" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B29" t="s">
-        <v>78</v>
-      </c>
-      <c r="I29">
-        <v>0</v>
-      </c>
-      <c r="J29">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="K29" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="L29" t="s">
         <v>16</v>
@@ -2019,22 +2352,16 @@
     </row>
     <row r="30" spans="1:13">
       <c r="A30" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="B30" t="s">
-        <v>80</v>
-      </c>
-      <c r="I30">
-        <v>0</v>
-      </c>
-      <c r="J30">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="K30" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="L30" t="s">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="M30" t="s">
         <v>16</v>
@@ -2042,22 +2369,16 @@
     </row>
     <row r="31" spans="1:13">
       <c r="A31" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B31" t="s">
-        <v>82</v>
-      </c>
-      <c r="I31">
-        <v>0</v>
-      </c>
-      <c r="J31">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="K31" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="L31" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="M31" t="s">
         <v>16</v>
@@ -2065,45 +2386,33 @@
     </row>
     <row r="32" spans="1:13">
       <c r="A32" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B32" t="s">
-        <v>84</v>
-      </c>
-      <c r="I32">
-        <v>0</v>
-      </c>
-      <c r="J32">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="K32" t="s">
-        <v>53</v>
+        <v>15</v>
       </c>
       <c r="L32" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="M32" t="s">
-        <v>59</v>
+        <v>16</v>
       </c>
     </row>
     <row r="33" spans="1:13">
       <c r="A33" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B33" t="s">
-        <v>86</v>
-      </c>
-      <c r="I33">
-        <v>0</v>
-      </c>
-      <c r="J33">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="K33" t="s">
-        <v>53</v>
+        <v>15</v>
       </c>
       <c r="L33" t="s">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="M33" t="s">
         <v>16</v>
@@ -2111,19 +2420,13 @@
     </row>
     <row r="34" spans="1:13">
       <c r="A34" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B34" t="s">
-        <v>88</v>
-      </c>
-      <c r="I34">
-        <v>0</v>
-      </c>
-      <c r="J34">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="K34" t="s">
-        <v>53</v>
+        <v>15</v>
       </c>
       <c r="L34" t="s">
         <v>16</v>
@@ -2134,22 +2437,16 @@
     </row>
     <row r="35" spans="1:13">
       <c r="A35" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="B35" t="s">
-        <v>90</v>
-      </c>
-      <c r="I35">
-        <v>0</v>
-      </c>
-      <c r="J35">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="K35" t="s">
-        <v>53</v>
+        <v>15</v>
       </c>
       <c r="L35" t="s">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="M35" t="s">
         <v>16</v>
@@ -2157,22 +2454,16 @@
     </row>
     <row r="36" spans="1:13">
       <c r="A36" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B36" t="s">
-        <v>92</v>
-      </c>
-      <c r="I36">
-        <v>0</v>
-      </c>
-      <c r="J36">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="K36" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="L36" t="s">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="M36" t="s">
         <v>16</v>
@@ -2180,19 +2471,13 @@
     </row>
     <row r="37" spans="1:13">
       <c r="A37" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="B37" t="s">
-        <v>94</v>
-      </c>
-      <c r="I37">
-        <v>0</v>
-      </c>
-      <c r="J37">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="K37" t="s">
-        <v>53</v>
+        <v>15</v>
       </c>
       <c r="L37" t="s">
         <v>16</v>
@@ -2203,16 +2488,10 @@
     </row>
     <row r="38" spans="1:13">
       <c r="A38" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B38" t="s">
-        <v>96</v>
-      </c>
-      <c r="I38">
-        <v>0</v>
-      </c>
-      <c r="J38">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="K38" t="s">
         <v>15</v>
@@ -2226,19 +2505,13 @@
     </row>
     <row r="39" spans="1:13">
       <c r="A39" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B39" t="s">
-        <v>98</v>
-      </c>
-      <c r="I39">
-        <v>0</v>
-      </c>
-      <c r="J39">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="K39" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="L39" t="s">
         <v>16</v>
@@ -2249,19 +2522,13 @@
     </row>
     <row r="40" spans="1:13">
       <c r="A40" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B40" t="s">
-        <v>100</v>
-      </c>
-      <c r="I40">
-        <v>0</v>
-      </c>
-      <c r="J40">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="K40" t="s">
-        <v>53</v>
+        <v>15</v>
       </c>
       <c r="L40" t="s">
         <v>16</v>
@@ -2272,42 +2539,30 @@
     </row>
     <row r="41" spans="1:13">
       <c r="A41" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="B41" t="s">
-        <v>102</v>
-      </c>
-      <c r="I41">
-        <v>0</v>
-      </c>
-      <c r="J41">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="K41" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L41" t="s">
         <v>16</v>
       </c>
       <c r="M41" t="s">
-        <v>103</v>
+        <v>16</v>
       </c>
     </row>
     <row r="42" spans="1:13">
       <c r="A42" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="B42" t="s">
-        <v>105</v>
-      </c>
-      <c r="I42">
-        <v>0</v>
-      </c>
-      <c r="J42">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="K42" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L42" t="s">
         <v>16</v>
@@ -2318,19 +2573,13 @@
     </row>
     <row r="43" spans="1:13">
       <c r="A43" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="B43" t="s">
-        <v>107</v>
-      </c>
-      <c r="I43">
-        <v>0</v>
-      </c>
-      <c r="J43">
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="K43" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L43" t="s">
         <v>16</v>
@@ -2341,42 +2590,30 @@
     </row>
     <row r="44" spans="1:13">
       <c r="A44" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="B44" t="s">
-        <v>109</v>
-      </c>
-      <c r="I44">
-        <v>0</v>
-      </c>
-      <c r="J44">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="K44" t="s">
-        <v>16</v>
+        <v>106</v>
       </c>
       <c r="L44" t="s">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="M44" t="s">
-        <v>16</v>
+        <v>107</v>
       </c>
     </row>
     <row r="45" spans="1:13">
       <c r="A45" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B45" t="s">
-        <v>111</v>
-      </c>
-      <c r="I45">
-        <v>0</v>
-      </c>
-      <c r="J45">
-        <v>0</v>
+        <v>109</v>
       </c>
       <c r="K45" t="s">
-        <v>16</v>
+        <v>106</v>
       </c>
       <c r="L45" t="s">
         <v>16</v>
@@ -2387,19 +2624,13 @@
     </row>
     <row r="46" spans="1:13">
       <c r="A46" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B46" t="s">
-        <v>113</v>
-      </c>
-      <c r="I46">
-        <v>0</v>
-      </c>
-      <c r="J46">
-        <v>0</v>
+        <v>111</v>
       </c>
       <c r="K46" t="s">
-        <v>16</v>
+        <v>106</v>
       </c>
       <c r="L46" t="s">
         <v>16</v>
@@ -2410,19 +2641,13 @@
     </row>
     <row r="47" spans="1:13">
       <c r="A47" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B47" t="s">
-        <v>115</v>
-      </c>
-      <c r="I47">
-        <v>0</v>
-      </c>
-      <c r="J47">
-        <v>0</v>
+        <v>113</v>
       </c>
       <c r="K47" t="s">
-        <v>16</v>
+        <v>106</v>
       </c>
       <c r="L47" t="s">
         <v>16</v>
@@ -2433,19 +2658,13 @@
     </row>
     <row r="48" spans="1:13">
       <c r="A48" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B48" t="s">
-        <v>117</v>
-      </c>
-      <c r="I48">
-        <v>0</v>
-      </c>
-      <c r="J48">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="K48" t="s">
-        <v>16</v>
+        <v>106</v>
       </c>
       <c r="L48" t="s">
         <v>16</v>
@@ -2456,22 +2675,16 @@
     </row>
     <row r="49" spans="1:13">
       <c r="A49" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B49" t="s">
-        <v>119</v>
-      </c>
-      <c r="I49">
-        <v>0</v>
-      </c>
-      <c r="J49">
-        <v>0</v>
+        <v>117</v>
       </c>
       <c r="K49" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L49" t="s">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="M49" t="s">
         <v>16</v>
@@ -2479,24 +2692,1463 @@
     </row>
     <row r="50" spans="1:13">
       <c r="A50" t="s">
+        <v>118</v>
+      </c>
+      <c r="B50" t="s">
+        <v>119</v>
+      </c>
+      <c r="K50" t="s">
+        <v>15</v>
+      </c>
+      <c r="L50" t="s">
+        <v>37</v>
+      </c>
+      <c r="M50" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13">
+      <c r="A51" t="s">
         <v>120</v>
       </c>
-      <c r="B50" t="s">
+      <c r="B51" t="s">
         <v>121</v>
       </c>
-      <c r="I50">
-        <v>0</v>
-      </c>
-      <c r="J50">
-        <v>0</v>
-      </c>
-      <c r="K50" t="s">
-        <v>16</v>
-      </c>
-      <c r="L50" t="s">
-        <v>16</v>
-      </c>
-      <c r="M50" t="s">
+      <c r="K51" t="s">
+        <v>15</v>
+      </c>
+      <c r="L51" t="s">
+        <v>16</v>
+      </c>
+      <c r="M51" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13">
+      <c r="A52" t="s">
+        <v>122</v>
+      </c>
+      <c r="B52" t="s">
+        <v>123</v>
+      </c>
+      <c r="K52" t="s">
+        <v>15</v>
+      </c>
+      <c r="L52" t="s">
+        <v>16</v>
+      </c>
+      <c r="M52" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13">
+      <c r="A53" t="s">
+        <v>124</v>
+      </c>
+      <c r="B53" t="s">
+        <v>125</v>
+      </c>
+      <c r="K53" t="s">
+        <v>15</v>
+      </c>
+      <c r="L53" t="s">
+        <v>16</v>
+      </c>
+      <c r="M53" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13">
+      <c r="A54" t="s">
+        <v>126</v>
+      </c>
+      <c r="B54" t="s">
+        <v>127</v>
+      </c>
+      <c r="K54" t="s">
+        <v>15</v>
+      </c>
+      <c r="L54" t="s">
+        <v>37</v>
+      </c>
+      <c r="M54" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13">
+      <c r="A55" t="s">
+        <v>128</v>
+      </c>
+      <c r="B55" t="s">
+        <v>129</v>
+      </c>
+      <c r="K55" t="s">
+        <v>15</v>
+      </c>
+      <c r="L55" t="s">
+        <v>37</v>
+      </c>
+      <c r="M55" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13">
+      <c r="A56" t="s">
+        <v>130</v>
+      </c>
+      <c r="B56" t="s">
+        <v>131</v>
+      </c>
+      <c r="K56" t="s">
+        <v>15</v>
+      </c>
+      <c r="L56" t="s">
+        <v>16</v>
+      </c>
+      <c r="M56" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13">
+      <c r="A57" t="s">
+        <v>132</v>
+      </c>
+      <c r="B57" t="s">
+        <v>129</v>
+      </c>
+      <c r="K57" t="s">
+        <v>15</v>
+      </c>
+      <c r="L57" t="s">
+        <v>16</v>
+      </c>
+      <c r="M57" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13">
+      <c r="A58" t="s">
+        <v>133</v>
+      </c>
+      <c r="B58" t="s">
+        <v>134</v>
+      </c>
+      <c r="K58" t="s">
+        <v>15</v>
+      </c>
+      <c r="L58" t="s">
+        <v>16</v>
+      </c>
+      <c r="M58" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13">
+      <c r="A59" t="s">
+        <v>135</v>
+      </c>
+      <c r="B59" t="s">
+        <v>136</v>
+      </c>
+      <c r="K59" t="s">
+        <v>15</v>
+      </c>
+      <c r="L59" t="s">
+        <v>37</v>
+      </c>
+      <c r="M59" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13">
+      <c r="A60" t="s">
+        <v>137</v>
+      </c>
+      <c r="B60" t="s">
+        <v>138</v>
+      </c>
+      <c r="K60" t="s">
+        <v>15</v>
+      </c>
+      <c r="L60" t="s">
+        <v>37</v>
+      </c>
+      <c r="M60" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13">
+      <c r="A61" t="s">
+        <v>139</v>
+      </c>
+      <c r="B61" t="s">
+        <v>71</v>
+      </c>
+      <c r="K61" t="s">
+        <v>15</v>
+      </c>
+      <c r="L61" t="s">
+        <v>37</v>
+      </c>
+      <c r="M61" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13">
+      <c r="A62" t="s">
+        <v>140</v>
+      </c>
+      <c r="B62" t="s">
+        <v>62</v>
+      </c>
+      <c r="K62" t="s">
+        <v>15</v>
+      </c>
+      <c r="L62" t="s">
+        <v>37</v>
+      </c>
+      <c r="M62" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13">
+      <c r="A63" t="s">
+        <v>141</v>
+      </c>
+      <c r="B63" t="s">
+        <v>142</v>
+      </c>
+      <c r="K63" t="s">
+        <v>106</v>
+      </c>
+      <c r="L63" t="s">
+        <v>37</v>
+      </c>
+      <c r="M63" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13">
+      <c r="A64" t="s">
+        <v>143</v>
+      </c>
+      <c r="B64" t="s">
+        <v>144</v>
+      </c>
+      <c r="K64" t="s">
+        <v>106</v>
+      </c>
+      <c r="L64" t="s">
+        <v>37</v>
+      </c>
+      <c r="M64" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13">
+      <c r="A65" t="s">
+        <v>145</v>
+      </c>
+      <c r="B65" t="s">
+        <v>146</v>
+      </c>
+      <c r="K65" t="s">
+        <v>36</v>
+      </c>
+      <c r="L65" t="s">
+        <v>37</v>
+      </c>
+      <c r="M65" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13">
+      <c r="A66" t="s">
+        <v>148</v>
+      </c>
+      <c r="B66" t="s">
+        <v>149</v>
+      </c>
+      <c r="K66" t="s">
+        <v>36</v>
+      </c>
+      <c r="L66" t="s">
+        <v>16</v>
+      </c>
+      <c r="M66" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13">
+      <c r="A67" t="s">
+        <v>150</v>
+      </c>
+      <c r="B67" t="s">
+        <v>151</v>
+      </c>
+      <c r="K67" t="s">
+        <v>36</v>
+      </c>
+      <c r="L67" t="s">
+        <v>16</v>
+      </c>
+      <c r="M67" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="68" spans="1:13">
+      <c r="A68" t="s">
+        <v>152</v>
+      </c>
+      <c r="B68" t="s">
+        <v>153</v>
+      </c>
+      <c r="K68" t="s">
+        <v>36</v>
+      </c>
+      <c r="L68" t="s">
+        <v>16</v>
+      </c>
+      <c r="M68" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="69" spans="1:13">
+      <c r="A69" t="s">
+        <v>154</v>
+      </c>
+      <c r="B69" t="s">
+        <v>155</v>
+      </c>
+      <c r="K69" t="s">
+        <v>36</v>
+      </c>
+      <c r="L69" t="s">
+        <v>16</v>
+      </c>
+      <c r="M69" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="70" spans="1:13">
+      <c r="A70" t="s">
+        <v>156</v>
+      </c>
+      <c r="B70" t="s">
+        <v>157</v>
+      </c>
+      <c r="K70" t="s">
+        <v>36</v>
+      </c>
+      <c r="L70" t="s">
+        <v>16</v>
+      </c>
+      <c r="M70" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="71" spans="1:13">
+      <c r="A71" t="s">
+        <v>158</v>
+      </c>
+      <c r="B71" t="s">
+        <v>159</v>
+      </c>
+      <c r="K71" t="s">
+        <v>36</v>
+      </c>
+      <c r="L71" t="s">
+        <v>16</v>
+      </c>
+      <c r="M71" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="72" spans="1:13">
+      <c r="A72" t="s">
+        <v>160</v>
+      </c>
+      <c r="B72" t="s">
+        <v>161</v>
+      </c>
+      <c r="K72" t="s">
+        <v>36</v>
+      </c>
+      <c r="L72" t="s">
+        <v>16</v>
+      </c>
+      <c r="M72" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="73" spans="1:13">
+      <c r="A73" t="s">
+        <v>162</v>
+      </c>
+      <c r="B73" t="s">
+        <v>163</v>
+      </c>
+      <c r="K73" t="s">
+        <v>36</v>
+      </c>
+      <c r="L73" t="s">
+        <v>16</v>
+      </c>
+      <c r="M73" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="74" spans="1:13">
+      <c r="A74" t="s">
+        <v>164</v>
+      </c>
+      <c r="B74" t="s">
+        <v>165</v>
+      </c>
+      <c r="K74" t="s">
+        <v>36</v>
+      </c>
+      <c r="L74" t="s">
+        <v>16</v>
+      </c>
+      <c r="M74" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="75" spans="1:13">
+      <c r="A75" t="s">
+        <v>166</v>
+      </c>
+      <c r="B75" t="s">
+        <v>167</v>
+      </c>
+      <c r="K75" t="s">
+        <v>36</v>
+      </c>
+      <c r="L75" t="s">
+        <v>16</v>
+      </c>
+      <c r="M75" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="76" spans="1:13">
+      <c r="A76" t="s">
+        <v>168</v>
+      </c>
+      <c r="B76" t="s">
+        <v>169</v>
+      </c>
+      <c r="K76" t="s">
+        <v>36</v>
+      </c>
+      <c r="L76" t="s">
+        <v>16</v>
+      </c>
+      <c r="M76" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="77" spans="1:13">
+      <c r="A77" t="s">
+        <v>170</v>
+      </c>
+      <c r="B77" t="s">
+        <v>171</v>
+      </c>
+      <c r="K77" t="s">
+        <v>36</v>
+      </c>
+      <c r="L77" t="s">
+        <v>16</v>
+      </c>
+      <c r="M77" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="78" spans="1:13">
+      <c r="A78" t="s">
+        <v>172</v>
+      </c>
+      <c r="B78" t="s">
+        <v>173</v>
+      </c>
+      <c r="K78" t="s">
+        <v>36</v>
+      </c>
+      <c r="L78" t="s">
+        <v>16</v>
+      </c>
+      <c r="M78" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="79" spans="1:13">
+      <c r="A79" t="s">
+        <v>174</v>
+      </c>
+      <c r="B79" t="s">
+        <v>175</v>
+      </c>
+      <c r="K79" t="s">
+        <v>36</v>
+      </c>
+      <c r="L79" t="s">
+        <v>16</v>
+      </c>
+      <c r="M79" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="80" spans="1:13">
+      <c r="A80" t="s">
+        <v>176</v>
+      </c>
+      <c r="B80" t="s">
+        <v>177</v>
+      </c>
+      <c r="K80" t="s">
+        <v>36</v>
+      </c>
+      <c r="L80" t="s">
+        <v>16</v>
+      </c>
+      <c r="M80" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="81" spans="1:13">
+      <c r="A81" t="s">
+        <v>178</v>
+      </c>
+      <c r="B81" t="s">
+        <v>179</v>
+      </c>
+      <c r="K81" t="s">
+        <v>36</v>
+      </c>
+      <c r="L81" t="s">
+        <v>16</v>
+      </c>
+      <c r="M81" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="82" spans="1:13">
+      <c r="A82" t="s">
+        <v>180</v>
+      </c>
+      <c r="B82" t="s">
+        <v>181</v>
+      </c>
+      <c r="K82" t="s">
+        <v>36</v>
+      </c>
+      <c r="L82" t="s">
+        <v>37</v>
+      </c>
+      <c r="M82" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="83" spans="1:13">
+      <c r="A83" t="s">
+        <v>182</v>
+      </c>
+      <c r="B83" t="s">
+        <v>183</v>
+      </c>
+      <c r="K83" t="s">
+        <v>36</v>
+      </c>
+      <c r="L83" t="s">
+        <v>37</v>
+      </c>
+      <c r="M83" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="84" spans="1:13">
+      <c r="A84" t="s">
+        <v>184</v>
+      </c>
+      <c r="B84" t="s">
+        <v>185</v>
+      </c>
+      <c r="K84" t="s">
+        <v>36</v>
+      </c>
+      <c r="L84" t="s">
+        <v>16</v>
+      </c>
+      <c r="M84" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="85" spans="1:13">
+      <c r="A85" t="s">
+        <v>186</v>
+      </c>
+      <c r="B85" t="s">
+        <v>187</v>
+      </c>
+      <c r="K85" t="s">
+        <v>36</v>
+      </c>
+      <c r="L85" t="s">
+        <v>16</v>
+      </c>
+      <c r="M85" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="86" spans="1:13">
+      <c r="A86" t="s">
+        <v>188</v>
+      </c>
+      <c r="B86" t="s">
+        <v>189</v>
+      </c>
+      <c r="K86" t="s">
+        <v>36</v>
+      </c>
+      <c r="L86" t="s">
+        <v>16</v>
+      </c>
+      <c r="M86" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="87" spans="1:13">
+      <c r="A87" t="s">
+        <v>190</v>
+      </c>
+      <c r="B87" t="s">
+        <v>191</v>
+      </c>
+      <c r="K87" t="s">
+        <v>36</v>
+      </c>
+      <c r="L87" t="s">
+        <v>37</v>
+      </c>
+      <c r="M87" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="88" spans="1:13">
+      <c r="A88" t="s">
+        <v>192</v>
+      </c>
+      <c r="B88" t="s">
+        <v>193</v>
+      </c>
+      <c r="K88" t="s">
+        <v>36</v>
+      </c>
+      <c r="L88" t="s">
+        <v>16</v>
+      </c>
+      <c r="M88" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="89" spans="1:13">
+      <c r="A89" t="s">
+        <v>194</v>
+      </c>
+      <c r="B89" t="s">
+        <v>195</v>
+      </c>
+      <c r="K89" t="s">
+        <v>36</v>
+      </c>
+      <c r="L89" t="s">
+        <v>37</v>
+      </c>
+      <c r="M89" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="90" spans="1:13">
+      <c r="A90" t="s">
+        <v>196</v>
+      </c>
+      <c r="B90" t="s">
+        <v>197</v>
+      </c>
+      <c r="K90" t="s">
+        <v>36</v>
+      </c>
+      <c r="L90" t="s">
+        <v>16</v>
+      </c>
+      <c r="M90" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="91" spans="1:13">
+      <c r="A91" t="s">
+        <v>198</v>
+      </c>
+      <c r="B91" t="s">
+        <v>199</v>
+      </c>
+      <c r="K91" t="s">
+        <v>36</v>
+      </c>
+      <c r="L91" t="s">
+        <v>16</v>
+      </c>
+      <c r="M91" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="92" spans="1:13">
+      <c r="A92" t="s">
+        <v>200</v>
+      </c>
+      <c r="B92" t="s">
+        <v>201</v>
+      </c>
+      <c r="K92" t="s">
+        <v>106</v>
+      </c>
+      <c r="L92" t="s">
+        <v>37</v>
+      </c>
+      <c r="M92" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="93" spans="1:13">
+      <c r="A93" t="s">
+        <v>202</v>
+      </c>
+      <c r="B93" t="s">
+        <v>203</v>
+      </c>
+      <c r="K93" t="s">
+        <v>106</v>
+      </c>
+      <c r="L93" t="s">
+        <v>37</v>
+      </c>
+      <c r="M93" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="94" spans="1:13">
+      <c r="A94" t="s">
+        <v>204</v>
+      </c>
+      <c r="B94" t="s">
+        <v>205</v>
+      </c>
+      <c r="K94" t="s">
+        <v>106</v>
+      </c>
+      <c r="L94" t="s">
+        <v>37</v>
+      </c>
+      <c r="M94" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="95" spans="1:13">
+      <c r="A95" t="s">
+        <v>206</v>
+      </c>
+      <c r="B95" t="s">
+        <v>207</v>
+      </c>
+      <c r="K95" t="s">
+        <v>106</v>
+      </c>
+      <c r="L95" t="s">
+        <v>16</v>
+      </c>
+      <c r="M95" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="96" spans="1:13">
+      <c r="A96" t="s">
+        <v>208</v>
+      </c>
+      <c r="B96" t="s">
+        <v>209</v>
+      </c>
+      <c r="K96" t="s">
+        <v>106</v>
+      </c>
+      <c r="L96" t="s">
+        <v>16</v>
+      </c>
+      <c r="M96" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="97" spans="1:13">
+      <c r="A97" t="s">
+        <v>210</v>
+      </c>
+      <c r="B97" t="s">
+        <v>211</v>
+      </c>
+      <c r="K97" t="s">
+        <v>106</v>
+      </c>
+      <c r="L97" t="s">
+        <v>16</v>
+      </c>
+      <c r="M97" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="98" spans="1:13">
+      <c r="A98" t="s">
+        <v>212</v>
+      </c>
+      <c r="B98" t="s">
+        <v>213</v>
+      </c>
+      <c r="K98" t="s">
+        <v>106</v>
+      </c>
+      <c r="L98" t="s">
+        <v>16</v>
+      </c>
+      <c r="M98" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="99" spans="1:13">
+      <c r="A99" t="s">
+        <v>214</v>
+      </c>
+      <c r="B99" t="s">
+        <v>215</v>
+      </c>
+      <c r="K99" t="s">
+        <v>106</v>
+      </c>
+      <c r="L99" t="s">
+        <v>37</v>
+      </c>
+      <c r="M99" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="100" spans="1:13">
+      <c r="A100" t="s">
+        <v>216</v>
+      </c>
+      <c r="B100" t="s">
+        <v>217</v>
+      </c>
+      <c r="K100" t="s">
+        <v>106</v>
+      </c>
+      <c r="L100" t="s">
+        <v>16</v>
+      </c>
+      <c r="M100" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="101" spans="1:13">
+      <c r="A101" t="s">
+        <v>218</v>
+      </c>
+      <c r="B101" t="s">
+        <v>219</v>
+      </c>
+      <c r="K101" t="s">
+        <v>106</v>
+      </c>
+      <c r="L101" t="s">
+        <v>16</v>
+      </c>
+      <c r="M101" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="102" spans="1:13">
+      <c r="A102" t="s">
+        <v>220</v>
+      </c>
+      <c r="B102" t="s">
+        <v>221</v>
+      </c>
+      <c r="K102" t="s">
+        <v>106</v>
+      </c>
+      <c r="L102" t="s">
+        <v>16</v>
+      </c>
+      <c r="M102" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="103" spans="1:13">
+      <c r="A103" t="s">
+        <v>222</v>
+      </c>
+      <c r="B103" t="s">
+        <v>223</v>
+      </c>
+      <c r="K103" t="s">
+        <v>106</v>
+      </c>
+      <c r="L103" t="s">
+        <v>16</v>
+      </c>
+      <c r="M103" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="104" spans="1:13">
+      <c r="A104" t="s">
+        <v>224</v>
+      </c>
+      <c r="B104" t="s">
+        <v>225</v>
+      </c>
+      <c r="K104" t="s">
+        <v>106</v>
+      </c>
+      <c r="L104" t="s">
+        <v>16</v>
+      </c>
+      <c r="M104" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="105" spans="1:13">
+      <c r="A105" t="s">
+        <v>226</v>
+      </c>
+      <c r="B105" t="s">
+        <v>227</v>
+      </c>
+      <c r="K105" t="s">
+        <v>106</v>
+      </c>
+      <c r="L105" t="s">
+        <v>16</v>
+      </c>
+      <c r="M105" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="106" spans="1:13">
+      <c r="A106" t="s">
+        <v>228</v>
+      </c>
+      <c r="B106" t="s">
+        <v>229</v>
+      </c>
+      <c r="K106" t="s">
+        <v>106</v>
+      </c>
+      <c r="L106" t="s">
+        <v>16</v>
+      </c>
+      <c r="M106" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="107" spans="1:13">
+      <c r="A107" t="s">
+        <v>230</v>
+      </c>
+      <c r="B107" t="s">
+        <v>231</v>
+      </c>
+      <c r="K107" t="s">
+        <v>16</v>
+      </c>
+      <c r="L107" t="s">
+        <v>16</v>
+      </c>
+      <c r="M107" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="108" spans="1:13">
+      <c r="A108" t="s">
+        <v>232</v>
+      </c>
+      <c r="B108" t="s">
+        <v>233</v>
+      </c>
+      <c r="K108" t="s">
+        <v>36</v>
+      </c>
+      <c r="L108" t="s">
+        <v>16</v>
+      </c>
+      <c r="M108" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="109" spans="1:13">
+      <c r="A109" t="s">
+        <v>234</v>
+      </c>
+      <c r="B109" t="s">
+        <v>235</v>
+      </c>
+      <c r="K109" t="s">
+        <v>106</v>
+      </c>
+      <c r="L109" t="s">
+        <v>16</v>
+      </c>
+      <c r="M109" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="110" spans="1:13">
+      <c r="A110" t="s">
+        <v>236</v>
+      </c>
+      <c r="B110" t="s">
+        <v>237</v>
+      </c>
+      <c r="K110" t="s">
+        <v>15</v>
+      </c>
+      <c r="L110" t="s">
+        <v>16</v>
+      </c>
+      <c r="M110" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="111" spans="1:13">
+      <c r="A111" t="s">
+        <v>238</v>
+      </c>
+      <c r="B111" t="s">
+        <v>239</v>
+      </c>
+      <c r="K111" t="s">
+        <v>36</v>
+      </c>
+      <c r="L111" t="s">
+        <v>16</v>
+      </c>
+      <c r="M111" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="112" spans="1:13">
+      <c r="A112" t="s">
+        <v>240</v>
+      </c>
+      <c r="B112" t="s">
+        <v>241</v>
+      </c>
+      <c r="K112" t="s">
+        <v>36</v>
+      </c>
+      <c r="L112" t="s">
+        <v>16</v>
+      </c>
+      <c r="M112" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="113" spans="1:13">
+      <c r="A113" t="s">
+        <v>242</v>
+      </c>
+      <c r="B113" t="s">
+        <v>243</v>
+      </c>
+      <c r="K113" t="s">
+        <v>36</v>
+      </c>
+      <c r="L113" t="s">
+        <v>16</v>
+      </c>
+      <c r="M113" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="114" spans="1:13">
+      <c r="A114" t="s">
+        <v>244</v>
+      </c>
+      <c r="B114" t="s">
+        <v>245</v>
+      </c>
+      <c r="K114" t="s">
+        <v>106</v>
+      </c>
+      <c r="L114" t="s">
+        <v>16</v>
+      </c>
+      <c r="M114" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="115" spans="1:13">
+      <c r="A115" t="s">
+        <v>246</v>
+      </c>
+      <c r="B115" t="s">
+        <v>247</v>
+      </c>
+      <c r="K115" t="s">
+        <v>106</v>
+      </c>
+      <c r="L115" t="s">
+        <v>16</v>
+      </c>
+      <c r="M115" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="116" spans="1:13">
+      <c r="A116" t="s">
+        <v>248</v>
+      </c>
+      <c r="B116" t="s">
+        <v>249</v>
+      </c>
+      <c r="K116" t="s">
+        <v>106</v>
+      </c>
+      <c r="L116" t="s">
+        <v>16</v>
+      </c>
+      <c r="M116" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="117" spans="1:13">
+      <c r="A117" t="s">
+        <v>250</v>
+      </c>
+      <c r="B117" t="s">
+        <v>251</v>
+      </c>
+      <c r="K117" t="s">
+        <v>16</v>
+      </c>
+      <c r="L117" t="s">
+        <v>16</v>
+      </c>
+      <c r="M117" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="118" spans="1:13">
+      <c r="A118" t="s">
+        <v>253</v>
+      </c>
+      <c r="B118" t="s">
+        <v>254</v>
+      </c>
+      <c r="K118" t="s">
+        <v>16</v>
+      </c>
+      <c r="L118" t="s">
+        <v>16</v>
+      </c>
+      <c r="M118" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="119" spans="1:13">
+      <c r="A119" t="s">
+        <v>255</v>
+      </c>
+      <c r="B119" t="s">
+        <v>256</v>
+      </c>
+      <c r="K119" t="s">
+        <v>16</v>
+      </c>
+      <c r="L119" t="s">
+        <v>16</v>
+      </c>
+      <c r="M119" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="120" spans="1:13">
+      <c r="A120" t="s">
+        <v>257</v>
+      </c>
+      <c r="B120" t="s">
+        <v>258</v>
+      </c>
+      <c r="K120" t="s">
+        <v>16</v>
+      </c>
+      <c r="L120" t="s">
+        <v>16</v>
+      </c>
+      <c r="M120" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="121" spans="1:13">
+      <c r="A121" t="s">
+        <v>259</v>
+      </c>
+      <c r="B121" t="s">
+        <v>260</v>
+      </c>
+      <c r="K121" t="s">
+        <v>16</v>
+      </c>
+      <c r="L121" t="s">
+        <v>16</v>
+      </c>
+      <c r="M121" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="122" spans="1:13">
+      <c r="A122" t="s">
+        <v>261</v>
+      </c>
+      <c r="B122" t="s">
+        <v>262</v>
+      </c>
+      <c r="K122" t="s">
+        <v>16</v>
+      </c>
+      <c r="L122" t="s">
+        <v>16</v>
+      </c>
+      <c r="M122" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="123" spans="1:13">
+      <c r="A123" t="s">
+        <v>263</v>
+      </c>
+      <c r="B123" t="s">
+        <v>264</v>
+      </c>
+      <c r="K123" t="s">
+        <v>16</v>
+      </c>
+      <c r="L123" t="s">
+        <v>16</v>
+      </c>
+      <c r="M123" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="124" spans="1:13">
+      <c r="A124" t="s">
+        <v>265</v>
+      </c>
+      <c r="B124" t="s">
+        <v>266</v>
+      </c>
+      <c r="K124" t="s">
+        <v>16</v>
+      </c>
+      <c r="L124" t="s">
+        <v>16</v>
+      </c>
+      <c r="M124" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="125" spans="1:13">
+      <c r="A125" t="s">
+        <v>267</v>
+      </c>
+      <c r="B125" t="s">
+        <v>268</v>
+      </c>
+      <c r="K125" t="s">
+        <v>16</v>
+      </c>
+      <c r="L125" t="s">
+        <v>16</v>
+      </c>
+      <c r="M125" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="126" spans="1:13">
+      <c r="A126" t="s">
+        <v>269</v>
+      </c>
+      <c r="B126" t="s">
+        <v>270</v>
+      </c>
+      <c r="K126" t="s">
+        <v>16</v>
+      </c>
+      <c r="L126" t="s">
+        <v>16</v>
+      </c>
+      <c r="M126" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="127" spans="1:13">
+      <c r="A127" t="s">
+        <v>271</v>
+      </c>
+      <c r="B127" t="s">
+        <v>272</v>
+      </c>
+      <c r="K127" t="s">
+        <v>16</v>
+      </c>
+      <c r="L127" t="s">
+        <v>16</v>
+      </c>
+      <c r="M127" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="128" spans="1:13">
+      <c r="A128" t="s">
+        <v>273</v>
+      </c>
+      <c r="B128" t="s">
+        <v>274</v>
+      </c>
+      <c r="K128" t="s">
+        <v>16</v>
+      </c>
+      <c r="L128" t="s">
+        <v>16</v>
+      </c>
+      <c r="M128" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="129" spans="1:13">
+      <c r="A129" t="s">
+        <v>275</v>
+      </c>
+      <c r="B129" t="s">
+        <v>276</v>
+      </c>
+      <c r="K129" t="s">
+        <v>16</v>
+      </c>
+      <c r="L129" t="s">
+        <v>16</v>
+      </c>
+      <c r="M129" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="130" spans="1:13">
+      <c r="A130" t="s">
+        <v>277</v>
+      </c>
+      <c r="B130" t="s">
+        <v>278</v>
+      </c>
+      <c r="K130" t="s">
+        <v>16</v>
+      </c>
+      <c r="L130" t="s">
+        <v>16</v>
+      </c>
+      <c r="M130" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="131" spans="1:13">
+      <c r="A131" t="s">
+        <v>279</v>
+      </c>
+      <c r="B131" t="s">
+        <v>280</v>
+      </c>
+      <c r="K131" t="s">
+        <v>16</v>
+      </c>
+      <c r="L131" t="s">
+        <v>16</v>
+      </c>
+      <c r="M131" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="132" spans="1:13">
+      <c r="A132" t="s">
+        <v>281</v>
+      </c>
+      <c r="B132" t="s">
+        <v>282</v>
+      </c>
+      <c r="K132" t="s">
+        <v>16</v>
+      </c>
+      <c r="L132" t="s">
+        <v>16</v>
+      </c>
+      <c r="M132" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="133" spans="1:13">
+      <c r="A133" t="s">
+        <v>283</v>
+      </c>
+      <c r="B133" t="s">
+        <v>284</v>
+      </c>
+      <c r="K133" t="s">
+        <v>16</v>
+      </c>
+      <c r="L133" t="s">
+        <v>16</v>
+      </c>
+      <c r="M133" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="134" spans="1:13">
+      <c r="A134" t="s">
+        <v>285</v>
+      </c>
+      <c r="B134" t="s">
+        <v>286</v>
+      </c>
+      <c r="K134" t="s">
+        <v>16</v>
+      </c>
+      <c r="L134" t="s">
+        <v>16</v>
+      </c>
+      <c r="M134" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="135" spans="1:13">
+      <c r="A135" t="s">
+        <v>287</v>
+      </c>
+      <c r="B135" t="s">
+        <v>288</v>
+      </c>
+      <c r="K135" t="s">
+        <v>16</v>
+      </c>
+      <c r="L135" t="s">
+        <v>16</v>
+      </c>
+      <c r="M135" t="s">
         <v>16</v>
       </c>
     </row>
